--- a/artfynd/A 35258-2024 artfynd.xlsx
+++ b/artfynd/A 35258-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>105479263</v>
+        <v>105479261</v>
       </c>
       <c r="B2" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>425377.7018522816</v>
+        <v>425408</v>
       </c>
       <c r="R2" t="n">
-        <v>6171071.172221882</v>
+        <v>6171031</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -752,19 +747,9 @@
           <t>2011-04-04</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2011-04-04</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,15 +780,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>105479261</v>
+        <v>105479262</v>
       </c>
       <c r="B3" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -839,10 +819,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>425408.1029727617</v>
+        <v>425383</v>
       </c>
       <c r="R3" t="n">
-        <v>6171031.75000407</v>
+        <v>6171054</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -872,19 +852,9 @@
           <t>2011-04-04</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2011-04-04</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,15 +885,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>105479262</v>
+        <v>105479263</v>
       </c>
       <c r="B4" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -959,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>425383.0609860825</v>
+        <v>425377</v>
       </c>
       <c r="R4" t="n">
-        <v>6171054.166576842</v>
+        <v>6171071</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -992,19 +957,9 @@
           <t>2011-04-04</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2011-04-04</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1035,15 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113963312</v>
+        <v>113963197</v>
       </c>
       <c r="B5" t="n">
-        <v>105292</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1079,10 +1029,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>425359</v>
+        <v>425505</v>
       </c>
       <c r="R5" t="n">
-        <v>6171075</v>
+        <v>6171045</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1109,17 +1059,17 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>c8eb7abf-a8e9-47e0-81c5-e2a98f916125</t>
+          <t>a2e3e22c-c2f6-4991-9407-2d71269ecc70</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-06-12</t>
+          <t>2023-06-15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-06-12</t>
+          <t>2023-06-15</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1150,15 +1100,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113963311</v>
+        <v>113963221</v>
       </c>
       <c r="B6" t="n">
-        <v>105292</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1194,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>425353</v>
+        <v>425447</v>
       </c>
       <c r="R6" t="n">
-        <v>6171074</v>
+        <v>6171161</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1224,24 +1169,24 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>6e347934-8ddc-4a4d-9c1d-98177af157d1</t>
+          <t>da1831f3-8d44-4859-aa50-d8516c44e96a</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-06-12</t>
+          <t>2023-06-14</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-06-12</t>
+          <t>2023-06-14</t>
         </is>
       </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="b">
         <v>0</v>
@@ -1265,15 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113963243</v>
+        <v>113963222</v>
       </c>
       <c r="B7" t="n">
-        <v>105292</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1309,10 +1249,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>425418</v>
+        <v>425424</v>
       </c>
       <c r="R7" t="n">
-        <v>6171204</v>
+        <v>6171167</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1339,7 +1279,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>6eab0658-8ce8-4882-93b9-31bb225ef5dc</t>
+          <t>4339bef3-0f0b-4eb0-b993-986f0f562c55</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1380,15 +1320,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113963222</v>
+        <v>113963230</v>
       </c>
       <c r="B8" t="n">
-        <v>105292</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1424,10 +1359,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>425424</v>
+        <v>425540</v>
       </c>
       <c r="R8" t="n">
-        <v>6171167</v>
+        <v>6171356</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1454,7 +1389,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>4339bef3-0f0b-4eb0-b993-986f0f562c55</t>
+          <t>66392c64-0e74-4d2b-9694-5bd356c8658b</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1465,6 +1400,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2023-06-14</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>2-stammigt på 1,3 meter. Mätt på 1 m.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1495,15 +1435,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113963230</v>
+        <v>113963243</v>
       </c>
       <c r="B9" t="n">
-        <v>105292</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,10 +1474,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>425540</v>
+        <v>425418</v>
       </c>
       <c r="R9" t="n">
-        <v>6171356</v>
+        <v>6171204</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1569,7 +1504,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>66392c64-0e74-4d2b-9694-5bd356c8658b</t>
+          <t>6eab0658-8ce8-4882-93b9-31bb225ef5dc</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1580,11 +1515,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2023-06-14</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>2-stammigt på 1,3 meter. Mätt på 1 m.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1615,15 +1545,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113963221</v>
+        <v>113963283</v>
       </c>
       <c r="B10" t="n">
-        <v>105292</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1659,10 +1584,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>425447</v>
+        <v>425270</v>
       </c>
       <c r="R10" t="n">
-        <v>6171161</v>
+        <v>6171240</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1684,22 +1609,22 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>Tolånga</t>
+          <t>Vollsjö</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>da1831f3-8d44-4859-aa50-d8516c44e96a</t>
+          <t>cf628f61-7cec-4f31-8b5c-16f3ffb47d5f</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-06-14</t>
+          <t>2023-06-13</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-06-14</t>
+          <t>2023-06-13</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1730,15 +1655,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113963197</v>
+        <v>113963311</v>
       </c>
       <c r="B11" t="n">
-        <v>105292</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1774,10 +1694,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>425505</v>
+        <v>425353</v>
       </c>
       <c r="R11" t="n">
-        <v>6171045</v>
+        <v>6171074</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1804,24 +1724,24 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>a2e3e22c-c2f6-4991-9407-2d71269ecc70</t>
+          <t>6e347934-8ddc-4a4d-9c1d-98177af157d1</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-06-15</t>
+          <t>2023-06-12</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-06-15</t>
+          <t>2023-06-12</t>
         </is>
       </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG11" t="b">
         <v>0</v>
@@ -1845,15 +1765,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113963313</v>
+        <v>113963312</v>
       </c>
       <c r="B12" t="n">
-        <v>105292</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1889,10 +1804,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>425415</v>
+        <v>425359</v>
       </c>
       <c r="R12" t="n">
-        <v>6171035</v>
+        <v>6171075</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1919,7 +1834,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>bad06241-359d-48bf-90d0-3b1cf096051d</t>
+          <t>c8eb7abf-a8e9-47e0-81c5-e2a98f916125</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -1960,15 +1875,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113963315</v>
+        <v>113963313</v>
       </c>
       <c r="B13" t="n">
-        <v>105292</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2004,10 +1914,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>425447</v>
+        <v>425415</v>
       </c>
       <c r="R13" t="n">
-        <v>6171019</v>
+        <v>6171035</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2034,7 +1944,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>20f9019b-fdcb-4aa1-b465-fb9b4ecca2e0</t>
+          <t>bad06241-359d-48bf-90d0-3b1cf096051d</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -2068,6 +1978,116 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr">
+        <is>
+          <t>Skyddsvärda träd</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>113963315</v>
+      </c>
+      <c r="B14" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Klasarödsgården, Sk</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>425447</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6171019</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Sjöbo</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Tolånga</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>20f9019b-fdcb-4aa1-b465-fb9b4ecca2e0</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2023-06-12</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2023-06-12</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Torbjörn Blixt</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Via Torbjörn Blixt</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
         <is>
           <t>Skyddsvärda träd</t>
         </is>
